--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343489</v>
       </c>
       <c r="B2" t="n">
-        <v>75158</v>
+        <v>75161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96266</v>
+        <v>96269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343489</v>
       </c>
       <c r="B2" t="n">
-        <v>75161</v>
+        <v>75187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96269</v>
+        <v>96295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96295</v>
+        <v>96296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96296</v>
+        <v>96297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343489</v>
       </c>
       <c r="B2" t="n">
-        <v>75187</v>
+        <v>75189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96297</v>
+        <v>96299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96299</v>
+        <v>96303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343489</v>
       </c>
       <c r="B2" t="n">
-        <v>75189</v>
+        <v>75197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96303</v>
+        <v>96316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343489</v>
       </c>
       <c r="B2" t="n">
-        <v>75197</v>
+        <v>75198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96316</v>
+        <v>96317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130343489</v>
       </c>
       <c r="B2" t="n">
-        <v>75198</v>
+        <v>75199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130343487</v>
       </c>
       <c r="B4" t="n">
-        <v>96317</v>
+        <v>96320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130343489</v>
+        <v>130343444</v>
       </c>
       <c r="B2" t="n">
-        <v>75199</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Onsjömyren, N om, Upl</t>
+          <t>Bredbäck, ca 1,5 km SO om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627271</v>
+        <v>626897</v>
       </c>
       <c r="R2" t="n">
-        <v>6691239</v>
+        <v>6691739</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -764,12 +764,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre blandsumpskog</t>
+          <t>äldre lövsumpskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,7 +790,7 @@
         <v>130343462</v>
       </c>
       <c r="B3" t="n">
-        <v>97220</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130343487</v>
+        <v>130343482</v>
       </c>
       <c r="B4" t="n">
-        <v>96320</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627253</v>
+        <v>627379</v>
       </c>
       <c r="R4" t="n">
-        <v>6691342</v>
+        <v>6691447</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>björklåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,6 +1008,1370 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130343488</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>627253</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6691252</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>låga av obestämt trädslag</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130343479</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96460</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Platt spretmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Herzogiella turfacea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Lindb.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>627502</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6691359</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>äldre barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130343487</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>627253</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691342</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>björklåga</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130343477</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>627511</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6691368</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130343486</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627389</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6691401</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130343478</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>627511</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6691370</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>äldre barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130343489</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>627271</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6691239</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130343491</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>627269</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6691185</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>medelålders gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130343463</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>627561</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6691289</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130343481</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>627412</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6691451</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>äldre blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130343461</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>627569</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6691059</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldre barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130343464</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Onsjömyren, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>627632</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6691288</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning Gysinge skog.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>äldre barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>björklåga</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47445-2025 artfynd.xlsx
+++ b/artfynd/A 47445-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343444</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343462</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343488</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343479</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343487</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343486</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343478</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343489</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343491</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2021,6 +2081,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343463</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2138,6 +2203,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343481</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343461</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2372,8 +2447,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130343464</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>